--- a/input/mapping/052. OCB_GOLD_TCKH_V_FTP_RATE_PHAT.xlsx
+++ b/input/mapping/052. OCB_GOLD_TCKH_V_FTP_RATE_PHAT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30327"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30410"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OCB\Zone_C\Code dev lại silver\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="579" documentId="13_ncr:1_{59B91070-12FC-497E-8E29-8A77D2FCFAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{45836679-9C28-48B6-B499-52F3D3F811A7}"/>
+  <xr:revisionPtr revIDLastSave="581" documentId="13_ncr:1_{59B91070-12FC-497E-8E29-8A77D2FCFAC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C690918-0566-4922-B5E0-300CED9FDA2F}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -41,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="521" uniqueCount="139">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="139">
   <si>
     <t>V_FTP_RATE —  Data Lineage Summary</t>
   </si>
@@ -221,7 +221,7 @@
     <t>FTP_RATE</t>
   </si>
   <si>
-    <t>FTP_PD_RATE</t>
+    <t xml:space="preserve">FTP_PD_RATE </t>
   </si>
   <si>
     <t>PD_FTP_RATE</t>
@@ -1748,14 +1748,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="217.5">
+    <row r="3" spans="1:3" ht="18.75">
       <c r="A3" s="29" t="s">
         <v>16</v>
       </c>
       <c r="B3" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>17</v>
       </c>
     </row>
@@ -1777,14 +1777,14 @@
       </c>
       <c r="C5" s="30"/>
     </row>
-    <row r="6" spans="1:3" ht="325.5">
+    <row r="6" spans="1:3" ht="18.75">
       <c r="A6" s="29" t="s">
         <v>18</v>
       </c>
       <c r="B6" s="30" t="s">
         <v>1</v>
       </c>
-      <c r="C6" s="29" t="s">
+      <c r="C6" s="30" t="s">
         <v>19</v>
       </c>
     </row>
@@ -2357,7 +2357,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
     <col min="1" max="1" width="30.28515625" bestFit="1" customWidth="1"/>
@@ -2367,7 +2367,7 @@
     <col min="5" max="5" width="19.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" customHeight="1">
+    <row r="1" spans="1:5" ht="30" customHeight="1">
       <c r="A1" s="64" t="s">
         <v>22</v>
       </c>
@@ -2376,7 +2376,7 @@
       <c r="D1" s="65"/>
       <c r="E1" s="65"/>
     </row>
-    <row r="2" spans="1:6">
+    <row r="2" spans="1:5">
       <c r="A2" s="15" t="s">
         <v>23</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
+    <row r="3" spans="1:5">
       <c r="A3" s="16">
         <v>1</v>
       </c>
@@ -2408,14 +2408,14 @@
         <v>28</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="15">
+    <row r="4" spans="1:5" ht="15">
       <c r="A4" s="1"/>
       <c r="B4" s="1"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:6" ht="14.45" customHeight="1">
+    <row r="5" spans="1:5" ht="14.45" customHeight="1">
       <c r="A5" s="65" t="s">
         <v>29</v>
       </c>
@@ -2424,7 +2424,7 @@
       <c r="D5" s="65"/>
       <c r="E5" s="65"/>
     </row>
-    <row r="6" spans="1:6" ht="15">
+    <row r="6" spans="1:5" ht="15">
       <c r="A6" s="15" t="s">
         <v>14</v>
       </c>
@@ -2441,7 +2441,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:5">
       <c r="A7" s="16" t="s">
         <v>1</v>
       </c>
@@ -2458,7 +2458,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:5">
       <c r="A8" s="16" t="s">
         <v>1</v>
       </c>
@@ -2475,7 +2475,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="15">
+    <row r="9" spans="1:5">
       <c r="A9" s="16" t="s">
         <v>1</v>
       </c>
@@ -2491,11 +2491,8 @@
       <c r="E9" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="F9" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15">
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="16" t="s">
         <v>1</v>
       </c>
@@ -2512,7 +2509,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:5">
       <c r="A11" s="16" t="s">
         <v>1</v>
       </c>
@@ -2529,7 +2526,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
+    <row r="12" spans="1:5">
       <c r="A12" s="16" t="s">
         <v>1</v>
       </c>
@@ -2546,7 +2543,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6" ht="80.25" customHeight="1">
+    <row r="13" spans="1:5" ht="80.25" customHeight="1">
       <c r="A13" s="16" t="s">
         <v>1</v>
       </c>
@@ -2563,21 +2560,21 @@
         <v>3</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:5">
       <c r="A14" s="2"/>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
       <c r="D14" s="2"/>
       <c r="E14" s="2"/>
     </row>
-    <row r="15" spans="1:6">
+    <row r="15" spans="1:5">
       <c r="A15" s="2"/>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:5">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="3"/>
